--- a/test/测试用例_李怀宇.xlsx
+++ b/test/测试用例_李怀宇.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11430" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="9830"/>
   </bookViews>
   <sheets>
     <sheet name="Information文档信息" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="127">
   <si>
     <r>
       <rPr>
@@ -1173,6 +1173,66 @@
     <t>NT</t>
   </si>
   <si>
+    <t>ST-AUTH-005</t>
+  </si>
+  <si>
+    <t>缺少大写字母的密码被拒绝</t>
+  </si>
+  <si>
+    <t>password="valid@123"</t>
+  </si>
+  <si>
+    <t>HTTP 422；密码校验失败，必须包含大写字母，数据库不新增用户。</t>
+  </si>
+  <si>
+    <t>等价类（缺失大写字母）</t>
+  </si>
+  <si>
+    <t>ST-AUTH-006</t>
+  </si>
+  <si>
+    <t>缺少小写字母的密码被拒绝</t>
+  </si>
+  <si>
+    <t>password="VALID@123"</t>
+  </si>
+  <si>
+    <t>HTTP 422；密码校验失败，必须包含小写字母，数据库不新增用户。</t>
+  </si>
+  <si>
+    <t>等价类（缺失小写字母）</t>
+  </si>
+  <si>
+    <t>ST-AUTH-007</t>
+  </si>
+  <si>
+    <t>缺少数字的密码被拒绝</t>
+  </si>
+  <si>
+    <t>password="Valid@Test"</t>
+  </si>
+  <si>
+    <t>HTTP 422；密码校验失败，必须包含数字，数据库不新增用户。</t>
+  </si>
+  <si>
+    <t>等价类（缺失数字）</t>
+  </si>
+  <si>
+    <t>ST-AUTH-008</t>
+  </si>
+  <si>
+    <t>缺少特殊字符的密码被拒绝</t>
+  </si>
+  <si>
+    <t>password="Valid1234"</t>
+  </si>
+  <si>
+    <t>HTTP 422；密码校验失败，必须包含特殊字符，数据库不新增用户。</t>
+  </si>
+  <si>
+    <t>等价类（缺失特殊字符）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2020,14 +2080,14 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="12"/>
+      <color indexed="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
+      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3099,7 +3159,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-4.06902697357981e-6</c:v>
+                  <c:v>-8.13808706125538e-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3766,7 +3826,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="25">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983036</v>
+        <v>-983032</v>
       </c>
       <c r="F13" s="22"/>
     </row>
@@ -4170,14 +4230,14 @@
       </c>
       <c r="C38" s="45">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D38" s="44" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="46">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-4.06902697357981e-6</v>
+        <v>-8.13808706125538e-6</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4240,7 +4300,7 @@
       </c>
       <c r="C43" s="55">
         <f>E13</f>
-        <v>-983036</v>
+        <v>-983032</v>
       </c>
       <c r="D43" s="56"/>
       <c r="E43" s="57"/>
@@ -4626,68 +4686,172 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:140">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+    <row r="6" ht="56" spans="1:140">
+      <c r="A6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="1:140">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
+    <row r="7" ht="56" spans="1:140">
+      <c r="A7" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="1:140">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
+    <row r="8" ht="56" spans="1:140">
+      <c r="A8" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>111</v>
+      </c>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="1:140">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
+    <row r="9" ht="56" spans="1:140">
+      <c r="A9" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>116</v>
+      </c>
       <c r="N9" s="16"/>
     </row>
     <row r="10" spans="1:140">
@@ -42601,7 +42765,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42611,7 +42775,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42620,7 +42784,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42629,7 +42793,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42638,7 +42802,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42647,7 +42811,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -42656,7 +42820,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -42665,7 +42829,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -42674,7 +42838,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -42683,7 +42847,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/test/测试用例_李怀宇.xlsx
+++ b/test/测试用例_李怀宇.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="9830"/>
+    <workbookView windowWidth="25600" windowHeight="9830" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Information文档信息" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="155">
   <si>
     <r>
       <rPr>
@@ -1233,6 +1233,90 @@
     <t>等价类（缺失特殊字符）</t>
   </si>
   <si>
+    <t>ST-AUTH-009</t>
+  </si>
+  <si>
+    <t>重复邮箱注册被拒绝</t>
+  </si>
+  <si>
+    <t>user01@example.com 已存在。</t>
+  </si>
+  <si>
+    <t>POST /api/v1/auth/register；email="user01@example.com"；password="Other@123"</t>
+  </si>
+  <si>
+    <t>调用注册接口，再次使用相同邮箱注册。</t>
+  </si>
+  <si>
+    <t>HTTP 400；detail 为 "Email already registered"；用户记录数量不增加。</t>
+  </si>
+  <si>
+    <t>场景法（重复注册）</t>
+  </si>
+  <si>
+    <t>ST-AUTH-010</t>
+  </si>
+  <si>
+    <t>用户登录</t>
+  </si>
+  <si>
+    <t>正确账号和密码登录成功</t>
+  </si>
+  <si>
+    <t>用户已注册且账号有效，get_user_by_email 返回合法用户</t>
+  </si>
+  <si>
+    <t>POST /api/v1/auth/login；username=user01@example.com，password=Valid@123。</t>
+  </si>
+  <si>
+    <t>提交登录请求，查询返回用户，调用 auth_api.login()，检查返回的 token</t>
+  </si>
+  <si>
+    <t>HTTP 200；返回 access_token、token_type=bearer、expires_at、is_admin；access_token 可被 verify_token 解码为用户 ID。</t>
+  </si>
+  <si>
+    <t>ST-AUTH-011</t>
+  </si>
+  <si>
+    <t>不存在的邮箱登录返回错误</t>
+  </si>
+  <si>
+    <t>数据库中不存在 nobody@example.com（用户不存在）。</t>
+  </si>
+  <si>
+    <t>POST /api/v1/auth/login；username=nobody@example.com；password=Valid@123。</t>
+  </si>
+  <si>
+    <t>调用登录接口，查询返回None，捕获异常。</t>
+  </si>
+  <si>
+    <t>HTTP 401；detail 为 "Incorrect email or password"；不暴露邮箱是否存在。</t>
+  </si>
+  <si>
+    <t>等价类（不存在用户）+ 安全场景</t>
+  </si>
+  <si>
+    <t>ST-AUTH-012</t>
+  </si>
+  <si>
+    <t>错误密码登录返回错误</t>
+  </si>
+  <si>
+    <t>user01@example.com 已注册，get_user_by_email 返回已存在用户。</t>
+  </si>
+  <si>
+    <t>POST /api/v1/auth/login；username=user01@example.com；password=Wrong@123。</t>
+  </si>
+  <si>
+    <t>调用登录接口，查询返回用户，调用 auth_api.login()，密码不正确，捕获异常</t>
+  </si>
+  <si>
+    <t>HTTP 401；detail 与邮箱不存在时相同，均为 "Incorrect email or password"；不返回 token。</t>
+  </si>
+  <si>
+    <t>等价类（错误凭据）+ 安全场景</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2080,14 +2164,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
+      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="12"/>
+      <color indexed="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3159,7 +3243,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-8.13808706125538e-6</c:v>
+                  <c:v>-1.2207180263431e-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3826,7 +3910,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="25">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983032</v>
+        <v>-983028</v>
       </c>
       <c r="F13" s="22"/>
     </row>
@@ -4230,14 +4314,14 @@
       </c>
       <c r="C38" s="45">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38" s="44" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="46">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-8.13808706125538e-6</v>
+        <v>-1.2207180263431e-5</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4300,7 +4384,7 @@
       </c>
       <c r="C43" s="55">
         <f>E13</f>
-        <v>-983032</v>
+        <v>-983028</v>
       </c>
       <c r="D43" s="56"/>
       <c r="E43" s="57"/>
@@ -4854,68 +4938,172 @@
       </c>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="1:140">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
+    <row r="10" ht="98" spans="1:140">
+      <c r="A10" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>123</v>
+      </c>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="1:140">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
+    <row r="11" ht="112" spans="1:140">
+      <c r="A11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>71</v>
+      </c>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="1:140">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
+    <row r="12" ht="84" spans="1:140">
+      <c r="A12" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>137</v>
+      </c>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="1:140">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
+    <row r="13" ht="84" spans="1:140">
+      <c r="A13" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>144</v>
+      </c>
       <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:140">
@@ -42765,7 +42953,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42775,7 +42963,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42784,7 +42972,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42793,7 +42981,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42802,7 +42990,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42811,7 +42999,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -42820,7 +43008,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -42829,7 +43017,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -42838,7 +43026,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -42847,7 +43035,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/test/测试用例_李怀宇.xlsx
+++ b/test/测试用例_李怀宇.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="187">
   <si>
     <r>
       <rPr>
@@ -1317,6 +1317,102 @@
     <t>等价类（错误凭据）+ 安全场景</t>
   </si>
   <si>
+    <t>ST-AUTH-013</t>
+  </si>
+  <si>
+    <t>当前用户</t>
+  </si>
+  <si>
+    <t>使用合法用户Token获取当前用户</t>
+  </si>
+  <si>
+    <t>已经取得 user01的合法用户 JWT。</t>
+  </si>
+  <si>
+    <t>GET /api/v1/auth/me；Authorization: Bearer &lt;valid-user-token&gt;。</t>
+  </si>
+  <si>
+    <t>携带合法 Token 请求当前用户接口，检查返回对象的 id、email、is_admin。</t>
+  </si>
+  <si>
+    <t>HTTP 200；返回id、email 与 token 所属用户一致；is_admin 按管理员邮箱白名单判定。</t>
+  </si>
+  <si>
+    <t>场景法（正常鉴权）</t>
+  </si>
+  <si>
+    <t>ST-AUTH-014</t>
+  </si>
+  <si>
+    <t>Token验证</t>
+  </si>
+  <si>
+    <t>过期或签名错误Token被拒绝</t>
+  </si>
+  <si>
+    <t>准备一个 expires_delta 为负值的过期Token，或使用不同密钥签名的伪造Token。</t>
+  </si>
+  <si>
+    <t>GET /api/v1/auth/me；Authorization: Bearer &lt;expired-or-forged-token&gt;。</t>
+  </si>
+  <si>
+    <t>分别携带过期 Token 和伪造 Token 发送请求，捕获异常并检查状态码与detail。</t>
+  </si>
+  <si>
+    <t>HTTP 401；detail 为 Invalid token；不查询或返回受保护数据。</t>
+  </si>
+  <si>
+    <t>等价类（过期/伪造凭据）+ 安全场景</t>
+  </si>
+  <si>
+    <t>ST-AUTH-015</t>
+  </si>
+  <si>
+    <t>用户会话创建</t>
+  </si>
+  <si>
+    <t>合法用户能够创建会话并同步创建对应Thread</t>
+  </si>
+  <si>
+    <t>已经取得合法用户的Token。</t>
+  </si>
+  <si>
+    <t>POST /api/v1/sessions?name=CourseTest；Authorization: Bearer &lt;user-token&gt;。</t>
+  </si>
+  <si>
+    <t>调用sessions_api.create_session创建会话；查询 session 表和 thread 表，核对返回的 session_id、thread_id、user_id、token。</t>
+  </si>
+  <si>
+    <t>HTTP 200；返回 UUID 格式的session_id 和会话 Token；session 与 thread 使用相同 ID，session.user_id 为当前用户；token 可解码为 session_id。</t>
+  </si>
+  <si>
+    <t>场景法（事务一致性）</t>
+  </si>
+  <si>
+    <t>ST-AUTH-016</t>
+  </si>
+  <si>
+    <t>管理员权限</t>
+  </si>
+  <si>
+    <t>普通用户不能访问平台管理功能</t>
+  </si>
+  <si>
+    <t>管理员白名单仅包含 admin@example.com；当前用户为 member@example.com。</t>
+  </si>
+  <si>
+    <t>调用 require_platform_admin(member)。</t>
+  </si>
+  <si>
+    <t>设置管理员白名单；执行管理员权限依赖校验，捕获异常并检查状态码与 detail。</t>
+  </si>
+  <si>
+    <t>HTTP 403；detail=Platform admin access required；不执行后续管理操作。</t>
+  </si>
+  <si>
+    <t>等价类（无权限用户）+ 安全场景</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2164,14 +2260,14 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="12"/>
+      <color indexed="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
+      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3243,7 +3339,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-1.2207180263431e-5</c:v>
+                  <c:v>-1.62763065805107e-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3910,7 +4006,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="25">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983028</v>
+        <v>-983024</v>
       </c>
       <c r="F13" s="22"/>
     </row>
@@ -4314,14 +4410,14 @@
       </c>
       <c r="C38" s="45">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D38" s="44" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="46">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-1.2207180263431e-5</v>
+        <v>-1.62763065805107e-5</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4384,7 +4480,7 @@
       </c>
       <c r="C43" s="55">
         <f>E13</f>
-        <v>-983028</v>
+        <v>-983024</v>
       </c>
       <c r="D43" s="56"/>
       <c r="E43" s="57"/>
@@ -5106,68 +5202,172 @@
       </c>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:140">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
+    <row r="14" ht="70" spans="1:140">
+      <c r="A14" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>152</v>
+      </c>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="1:140">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
+    <row r="15" ht="70" spans="1:140">
+      <c r="A15" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>160</v>
+      </c>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="1:140">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
+    <row r="16" ht="112" spans="1:140">
+      <c r="A16" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>168</v>
+      </c>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
+    <row r="17" ht="56" spans="1:14">
+      <c r="A17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="N17" s="16"/>
     </row>
     <row r="18" spans="1:14">
@@ -42953,7 +43153,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42963,7 +43163,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42972,7 +43172,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42981,7 +43181,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42990,7 +43190,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42999,7 +43199,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -43008,7 +43208,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -43017,7 +43217,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -43026,7 +43226,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -43035,7 +43235,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/test/测试用例_李怀宇.xlsx
+++ b/test/测试用例_李怀宇.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="196">
   <si>
     <r>
       <rPr>
@@ -1411,6 +1411,33 @@
   </si>
   <si>
     <t>等价类（无权限用户）+ 安全场景</t>
+  </si>
+  <si>
+    <t>ST-AUTH-017</t>
+  </si>
+  <si>
+    <t>邮箱大小写归一化</t>
+  </si>
+  <si>
+    <t>注册和登录时邮箱应该统一转小写</t>
+  </si>
+  <si>
+    <t>数据库可用；邮箱 User01@Example.com尚未注册；测试中不连接真实数据库，不调用外部服务。</t>
+  </si>
+  <si>
+    <t>注册邮箱 User01@Example.com、密码 Valid@123；登录账号 User01@Example.com、密码 Valid@123</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 先用大小写混合的邮箱 User01@Example.com 进行注册；然后使用同一邮箱登录；检查注册与登录的过程中系统实际使用的邮箱</t>
+  </si>
+  <si>
+    <t>注册时候查库和存库应该使用的邮箱均为小写 user01@example.com；登录时查库应该使用的邮箱也为小写 user01@example.com</t>
+  </si>
+  <si>
+    <t>FAILED。注册时查库使用了原始大小写 User01@Example.com，未进行转小写。</t>
+  </si>
+  <si>
+    <t>等价类（大小写）+ 场景法</t>
   </si>
   <si>
     <r>
@@ -3339,13 +3366,13 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-1.62763065805107e-5</c:v>
+                  <c:v>-1.62763231379123e-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-1.01727019611952e-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4006,7 +4033,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="25">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983024</v>
+        <v>-983023</v>
       </c>
       <c r="F13" s="22"/>
     </row>
@@ -4417,7 +4444,7 @@
       </c>
       <c r="E38" s="46">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-1.62763065805107e-5</v>
+        <v>-1.62763231379123e-5</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4442,14 +4469,14 @@
       </c>
       <c r="C40" s="45">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="44" t="s">
         <v>42</v>
       </c>
       <c r="E40" s="46">
         <f>IF(E13=0,0,C40/E13)</f>
-        <v>0</v>
+        <v>-1.01727019611952e-6</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -4480,7 +4507,7 @@
       </c>
       <c r="C43" s="55">
         <f>E13</f>
-        <v>-983024</v>
+        <v>-983023</v>
       </c>
       <c r="D43" s="56"/>
       <c r="E43" s="57"/>
@@ -5370,20 +5397,42 @@
       </c>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+    <row r="18" ht="98" spans="1:14">
+      <c r="A18" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>62</v>
+      </c>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
+      <c r="G18" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>185</v>
+      </c>
       <c r="N18" s="16"/>
     </row>
     <row r="19" spans="1:14">
@@ -43153,7 +43202,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -43163,7 +43212,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -43172,7 +43221,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -43181,7 +43230,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -43190,7 +43239,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -43199,7 +43248,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -43208,7 +43257,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -43217,7 +43266,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -43226,7 +43275,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -43235,7 +43284,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
